--- a/simulacaoes_/lote_eixos_1p5/simulacao_C_18/design_variables_statistics.xlsx
+++ b/simulacaoes_/lote_eixos_1p5/simulacao_C_18/design_variables_statistics.xlsx
@@ -495,31 +495,31 @@
         <v>50</v>
       </c>
       <c r="C2" t="n">
-        <v>71.31</v>
+        <v>72.2</v>
       </c>
       <c r="D2" t="n">
-        <v>16.25</v>
+        <v>14.58</v>
       </c>
       <c r="E2" t="n">
-        <v>22.79</v>
+        <v>20.19</v>
       </c>
       <c r="F2" t="n">
-        <v>50.71</v>
+        <v>52.89</v>
       </c>
       <c r="G2" t="n">
-        <v>55.77</v>
+        <v>58.83</v>
       </c>
       <c r="H2" t="n">
-        <v>69.18000000000001</v>
+        <v>70.02</v>
       </c>
       <c r="I2" t="n">
-        <v>85.81999999999999</v>
+        <v>85.23</v>
       </c>
       <c r="J2" t="n">
         <v>100</v>
       </c>
       <c r="K2" t="n">
-        <v>49.29</v>
+        <v>47.11</v>
       </c>
     </row>
     <row r="3">
@@ -532,31 +532,31 @@
         <v>50</v>
       </c>
       <c r="C3" t="n">
-        <v>49.11</v>
+        <v>45.37</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6</v>
+        <v>0.66</v>
       </c>
       <c r="E3" t="n">
-        <v>1.21</v>
+        <v>1.46</v>
       </c>
       <c r="F3" t="n">
-        <v>46.48</v>
+        <v>41.56</v>
       </c>
       <c r="G3" t="n">
-        <v>48.79</v>
+        <v>45.42</v>
       </c>
       <c r="H3" t="n">
-        <v>49.05</v>
+        <v>45.43</v>
       </c>
       <c r="I3" t="n">
-        <v>49.44</v>
+        <v>45.45</v>
       </c>
       <c r="J3" t="n">
-        <v>49.96</v>
+        <v>46.68</v>
       </c>
       <c r="K3" t="n">
-        <v>3.48</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="4">
@@ -569,31 +569,31 @@
         <v>50</v>
       </c>
       <c r="C4" t="n">
-        <v>9.529999999999999</v>
+        <v>10.06</v>
       </c>
       <c r="D4" t="n">
-        <v>1.59</v>
+        <v>1.26</v>
       </c>
       <c r="E4" t="n">
-        <v>16.71</v>
+        <v>12.54</v>
       </c>
       <c r="F4" t="n">
-        <v>6.04</v>
+        <v>7.23</v>
       </c>
       <c r="G4" t="n">
-        <v>8.039999999999999</v>
+        <v>8.93</v>
       </c>
       <c r="H4" t="n">
-        <v>9.9</v>
+        <v>10.05</v>
       </c>
       <c r="I4" t="n">
-        <v>11.03</v>
+        <v>11.21</v>
       </c>
       <c r="J4" t="n">
-        <v>11.28</v>
+        <v>11.54</v>
       </c>
       <c r="K4" t="n">
-        <v>5.24</v>
+        <v>4.31</v>
       </c>
     </row>
     <row r="5">
@@ -606,31 +606,31 @@
         <v>50</v>
       </c>
       <c r="C5" t="n">
-        <v>152.04</v>
+        <v>108.22</v>
       </c>
       <c r="D5" t="n">
-        <v>10.64</v>
+        <v>11.69</v>
       </c>
       <c r="E5" t="n">
-        <v>7</v>
+        <v>10.8</v>
       </c>
       <c r="F5" t="n">
-        <v>130</v>
+        <v>86.23</v>
       </c>
       <c r="G5" t="n">
-        <v>145.36</v>
+        <v>104.06</v>
       </c>
       <c r="H5" t="n">
-        <v>149.19</v>
+        <v>110.37</v>
       </c>
       <c r="I5" t="n">
-        <v>155.73</v>
+        <v>114.02</v>
       </c>
       <c r="J5" t="n">
-        <v>176.78</v>
+        <v>134.24</v>
       </c>
       <c r="K5" t="n">
-        <v>46.78</v>
+        <v>48.01</v>
       </c>
     </row>
     <row r="6">
@@ -643,31 +643,31 @@
         <v>50</v>
       </c>
       <c r="C6" t="n">
-        <v>3.91</v>
+        <v>4.45</v>
       </c>
       <c r="D6" t="n">
-        <v>0.66</v>
+        <v>0.36</v>
       </c>
       <c r="E6" t="n">
-        <v>16.83</v>
+        <v>8.15</v>
       </c>
       <c r="F6" t="n">
-        <v>2.31</v>
+        <v>3.84</v>
       </c>
       <c r="G6" t="n">
-        <v>3.51</v>
+        <v>4.15</v>
       </c>
       <c r="H6" t="n">
-        <v>3.92</v>
+        <v>4.43</v>
       </c>
       <c r="I6" t="n">
-        <v>4.55</v>
+        <v>4.79</v>
       </c>
       <c r="J6" t="n">
-        <v>4.98</v>
+        <v>4.99</v>
       </c>
       <c r="K6" t="n">
-        <v>2.67</v>
+        <v>1.15</v>
       </c>
     </row>
   </sheetData>
